--- a/Embalses2026.xlsx
+++ b/Embalses2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Andres_Tobon\Desktop\Proyecto_Pronostico precios\Datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{161264D4-05FB-4CFD-A959-C729A54316EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F5136F8-B8C6-4050-A38D-EA54B72E972D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3855,7 +3855,40 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="9">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -3904,6 +3937,33 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC8DAB9"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
       <border>
         <left style="thin">
           <color auto="1"/>
@@ -3932,33 +3992,6 @@
         <right/>
         <top/>
         <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd"/>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC8DAB9"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
         <vertical/>
         <horizontal/>
       </border>
@@ -4263,7 +4296,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F1978"/>
+  <dimension ref="A1:F2040"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.6640625" customWidth="1"/>
@@ -20096,39 +20129,545 @@
         <v>68.822500000000005</v>
       </c>
     </row>
+    <row r="1979" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1979" s="5">
+        <v>46173</v>
+      </c>
+      <c r="B1979" s="1">
+        <v>69.069999999999993</v>
+      </c>
+    </row>
+    <row r="1980" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1980" s="5">
+        <v>46174</v>
+      </c>
+      <c r="B1980" s="1">
+        <v>69.11</v>
+      </c>
+    </row>
+    <row r="1981" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1981" s="5">
+        <v>46175</v>
+      </c>
+      <c r="B1981" s="1">
+        <v>69.34</v>
+      </c>
+    </row>
+    <row r="1982" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1982" s="5">
+        <v>46176</v>
+      </c>
+      <c r="B1982" s="1">
+        <v>69.5</v>
+      </c>
+    </row>
+    <row r="1983" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1983" s="5">
+        <v>46177</v>
+      </c>
+      <c r="B1983" s="1">
+        <v>69.7</v>
+      </c>
+    </row>
+    <row r="1984" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1984" s="5">
+        <v>46178</v>
+      </c>
+      <c r="B1984" s="1">
+        <v>70.45</v>
+      </c>
+    </row>
+    <row r="1985" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1985" s="5">
+        <v>46179</v>
+      </c>
+      <c r="B1985" s="1">
+        <v>71.040000000000006</v>
+      </c>
+    </row>
+    <row r="1986" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1986" s="5">
+        <v>46180</v>
+      </c>
+      <c r="B1986" s="1">
+        <v>71.849999999999994</v>
+      </c>
+    </row>
+    <row r="1987" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1987" s="5">
+        <v>46181</v>
+      </c>
+      <c r="B1987" s="1">
+        <v>72.81</v>
+      </c>
+    </row>
+    <row r="1988" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1988" s="5">
+        <v>46182</v>
+      </c>
+      <c r="B1988" s="1">
+        <v>73.25</v>
+      </c>
+    </row>
+    <row r="1989" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1989" s="5">
+        <v>46183</v>
+      </c>
+      <c r="B1989" s="1">
+        <v>73.7</v>
+      </c>
+    </row>
+    <row r="1990" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1990" s="5">
+        <v>46184</v>
+      </c>
+      <c r="B1990" s="1">
+        <v>73.569999999999993</v>
+      </c>
+    </row>
+    <row r="1991" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1991" s="5">
+        <v>46185</v>
+      </c>
+      <c r="B1991" s="1">
+        <v>73.28</v>
+      </c>
+    </row>
+    <row r="1992" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1992" s="5">
+        <v>46186</v>
+      </c>
+      <c r="B1992" s="1">
+        <v>73.040000000000006</v>
+      </c>
+    </row>
+    <row r="1993" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1993" s="5">
+        <v>46187</v>
+      </c>
+      <c r="B1993" s="1">
+        <v>73.34</v>
+      </c>
+    </row>
+    <row r="1994" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1994" s="5">
+        <v>46188</v>
+      </c>
+      <c r="B1994" s="1">
+        <v>73.44</v>
+      </c>
+    </row>
+    <row r="1995" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1995" s="5">
+        <v>46189</v>
+      </c>
+      <c r="B1995" s="1">
+        <v>73.55</v>
+      </c>
+    </row>
+    <row r="1996" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1996" s="5">
+        <v>46190</v>
+      </c>
+      <c r="B1996" s="1">
+        <v>73.62</v>
+      </c>
+    </row>
+    <row r="1997" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1997" s="5">
+        <v>46191</v>
+      </c>
+      <c r="B1997" s="1">
+        <v>73.930000000000007</v>
+      </c>
+    </row>
+    <row r="1998" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1998" s="5">
+        <v>46192</v>
+      </c>
+      <c r="B1998" s="1">
+        <v>74.13</v>
+      </c>
+    </row>
+    <row r="1999" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1999" s="5">
+        <v>46193</v>
+      </c>
+      <c r="B1999" s="1">
+        <v>74.25</v>
+      </c>
+    </row>
+    <row r="2000" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2000" s="5">
+        <v>46194</v>
+      </c>
+      <c r="B2000" s="1">
+        <v>74.64</v>
+      </c>
+    </row>
+    <row r="2001" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2001" s="5">
+        <v>46195</v>
+      </c>
+      <c r="B2001" s="1">
+        <v>74.760000000000005</v>
+      </c>
+    </row>
+    <row r="2002" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2002" s="5">
+        <v>46196</v>
+      </c>
+      <c r="B2002" s="1">
+        <v>75.38</v>
+      </c>
+    </row>
+    <row r="2003" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2003" s="5">
+        <v>46197</v>
+      </c>
+      <c r="B2003" s="1">
+        <v>75.3</v>
+      </c>
+    </row>
+    <row r="2004" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2004" s="5">
+        <v>46198</v>
+      </c>
+      <c r="B2004" s="1">
+        <v>75.040000000000006</v>
+      </c>
+    </row>
+    <row r="2005" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2005" s="5">
+        <v>46199</v>
+      </c>
+      <c r="B2005" s="1">
+        <v>74.86</v>
+      </c>
+    </row>
+    <row r="2006" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2006" s="5">
+        <v>46200</v>
+      </c>
+      <c r="B2006" s="1">
+        <v>74.739999999999995</v>
+      </c>
+    </row>
+    <row r="2007" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2007" s="5">
+        <v>46201</v>
+      </c>
+      <c r="B2007" s="1">
+        <v>75.16</v>
+      </c>
+    </row>
+    <row r="2008" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2008" s="5">
+        <v>46202</v>
+      </c>
+      <c r="B2008" s="1">
+        <v>75.37</v>
+      </c>
+    </row>
+    <row r="2009" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2009" s="5">
+        <v>46203</v>
+      </c>
+      <c r="B2009" s="1">
+        <v>76.42</v>
+      </c>
+    </row>
+    <row r="2010" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2010" s="5">
+        <v>46204</v>
+      </c>
+      <c r="B2010" s="1">
+        <v>76.459999999999994</v>
+      </c>
+    </row>
+    <row r="2011" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2011" s="5">
+        <v>46205</v>
+      </c>
+      <c r="B2011" s="1">
+        <v>76.84</v>
+      </c>
+    </row>
+    <row r="2012" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2012" s="5">
+        <v>46206</v>
+      </c>
+      <c r="B2012" s="1">
+        <v>77.38</v>
+      </c>
+    </row>
+    <row r="2013" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2013" s="5">
+        <v>46207</v>
+      </c>
+      <c r="B2013" s="1">
+        <v>77.900000000000006</v>
+      </c>
+    </row>
+    <row r="2014" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2014" s="5">
+        <v>46208</v>
+      </c>
+      <c r="B2014" s="1">
+        <v>78.23</v>
+      </c>
+    </row>
+    <row r="2015" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2015" s="5">
+        <v>46209</v>
+      </c>
+      <c r="B2015" s="1">
+        <v>78.260000000000005</v>
+      </c>
+    </row>
+    <row r="2016" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2016" s="5">
+        <v>46210</v>
+      </c>
+      <c r="B2016" s="1">
+        <v>78.17</v>
+      </c>
+    </row>
+    <row r="2017" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2017" s="5">
+        <v>46211</v>
+      </c>
+      <c r="B2017" s="1">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="2018" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2018" s="5">
+        <v>46212</v>
+      </c>
+      <c r="B2018" s="1">
+        <v>78.41</v>
+      </c>
+    </row>
+    <row r="2019" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2019" s="5">
+        <v>46213</v>
+      </c>
+      <c r="B2019" s="1">
+        <v>78.44</v>
+      </c>
+    </row>
+    <row r="2020" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2020" s="5">
+        <v>46214</v>
+      </c>
+      <c r="B2020" s="1">
+        <v>78.510000000000005</v>
+      </c>
+    </row>
+    <row r="2021" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2021" s="5">
+        <v>46215</v>
+      </c>
+      <c r="B2021" s="1">
+        <v>78.790000000000006</v>
+      </c>
+    </row>
+    <row r="2022" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2022" s="5">
+        <v>46216</v>
+      </c>
+      <c r="B2022" s="1">
+        <v>78.91</v>
+      </c>
+    </row>
+    <row r="2023" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2023" s="5">
+        <v>46217</v>
+      </c>
+      <c r="B2023" s="1">
+        <v>78.790000000000006</v>
+      </c>
+    </row>
+    <row r="2024" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2024" s="5">
+        <v>46218</v>
+      </c>
+      <c r="B2024" s="1">
+        <v>78.87</v>
+      </c>
+    </row>
+    <row r="2025" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2025" s="5">
+        <v>46219</v>
+      </c>
+      <c r="B2025" s="1">
+        <v>78.81</v>
+      </c>
+    </row>
+    <row r="2026" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2026" s="5">
+        <v>46220</v>
+      </c>
+      <c r="B2026" s="1">
+        <v>78.64</v>
+      </c>
+    </row>
+    <row r="2027" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2027" s="5">
+        <v>46221</v>
+      </c>
+      <c r="B2027" s="1">
+        <v>78.73</v>
+      </c>
+    </row>
+    <row r="2028" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2028" s="5">
+        <v>46222</v>
+      </c>
+      <c r="B2028" s="1">
+        <v>78.94</v>
+      </c>
+    </row>
+    <row r="2029" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2029" s="5">
+        <v>46223</v>
+      </c>
+      <c r="B2029" s="1">
+        <v>79.27</v>
+      </c>
+    </row>
+    <row r="2030" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2030" s="5">
+        <v>46224</v>
+      </c>
+      <c r="B2030" s="1">
+        <v>79.42</v>
+      </c>
+    </row>
+    <row r="2031" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2031" s="5">
+        <v>46225</v>
+      </c>
+      <c r="B2031" s="1">
+        <v>79.31</v>
+      </c>
+    </row>
+    <row r="2032" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2032" s="5">
+        <v>46226</v>
+      </c>
+      <c r="B2032" s="1">
+        <v>80.180000000000007</v>
+      </c>
+    </row>
+    <row r="2033" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2033" s="5">
+        <v>46227</v>
+      </c>
+      <c r="B2033" s="1">
+        <v>80.489999999999995</v>
+      </c>
+    </row>
+    <row r="2034" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2034" s="5">
+        <v>46228</v>
+      </c>
+      <c r="B2034" s="1">
+        <v>80.58</v>
+      </c>
+    </row>
+    <row r="2035" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2035" s="5">
+        <v>46229</v>
+      </c>
+      <c r="B2035" s="1">
+        <v>80.81</v>
+      </c>
+    </row>
+    <row r="2036" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2036" s="5">
+        <v>46230</v>
+      </c>
+      <c r="B2036" s="1">
+        <v>80.66</v>
+      </c>
+    </row>
+    <row r="2037" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2037" s="5">
+        <v>46231</v>
+      </c>
+      <c r="B2037" s="1">
+        <v>80.400000000000006</v>
+      </c>
+    </row>
+    <row r="2038" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2038" s="5">
+        <v>46232</v>
+      </c>
+      <c r="B2038" s="1">
+        <v>80.3</v>
+      </c>
+    </row>
+    <row r="2039" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2039" s="5">
+        <v>46233</v>
+      </c>
+      <c r="B2039" s="1">
+        <v>80.22</v>
+      </c>
+    </row>
+    <row r="2040" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2040" s="5">
+        <v>46234</v>
+      </c>
+      <c r="B2040" s="1">
+        <v>79.989999999999995</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A1978">
-    <cfRule type="cellIs" dxfId="6" priority="3" operator="notEqual">
+  <conditionalFormatting sqref="A2:A1093 A153:B1247">
+    <cfRule type="cellIs" dxfId="8" priority="9" operator="equal">
       <formula>""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A153:B1247 A2:A1093">
-    <cfRule type="cellIs" dxfId="5" priority="7" operator="equal">
+  <conditionalFormatting sqref="A2:A1093 A153:B1978">
+    <cfRule type="cellIs" dxfId="7" priority="4" operator="notEqual">
       <formula>""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A153:B1978 A2:A1093">
-    <cfRule type="cellIs" dxfId="4" priority="2" operator="notEqual">
+  <conditionalFormatting sqref="A2:A2040">
+    <cfRule type="cellIs" dxfId="6" priority="5" operator="notEqual">
       <formula>""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1248:B1612">
-    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
       <formula>""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1613:B1978">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="3" operator="equal">
       <formula>""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:C152">
-    <cfRule type="cellIs" dxfId="1" priority="17" operator="notEqual">
+    <cfRule type="cellIs" dxfId="3" priority="19" operator="notEqual">
       <formula>""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:XFD152 C153:XFD1978 A1979:XFD1048576">
-    <cfRule type="cellIs" dxfId="0" priority="16" operator="equal">
+  <conditionalFormatting sqref="A1:XFD152 C153:XFD1978 A2041:XFD1048576 B1979:XFD2040">
+    <cfRule type="cellIs" dxfId="2" priority="18" operator="equal">
+      <formula>""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1979:A2040">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="notEqual">
+      <formula>""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1979:A2040">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>""</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20137,21 +20676,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101000B5E555C9559504487B44633D1ADABB0" ma:contentTypeVersion="1" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="d749631d88defeecea5a3f1c2489276b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e48ec5c2-614c-49e6-a81a-ca54d4b077b0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="acf7ea99d1f8bcbadb4a28bdb40ccc60" ns2:_="">
     <xsd:import namespace="e48ec5c2-614c-49e6-a81a-ca54d4b077b0"/>
@@ -20291,24 +20815,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CCB5007D-D460-4EE4-9CD2-ECAD13EEA918}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0E140629-BDF3-4EFD-BD87-34341C160118}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{866447FC-0B76-4F06-A0DE-C3F04ABAD51C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -20324,4 +20846,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0E140629-BDF3-4EFD-BD87-34341C160118}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CCB5007D-D460-4EE4-9CD2-ECAD13EEA918}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>